--- a/data/programaciones-armas.xlsx
+++ b/data/programaciones-armas.xlsx
@@ -1,58 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,18 +45,94 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -150,7 +211,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -185,7 +245,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -220,16 +279,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -351,253 +414,381 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>id_registro</v>
-      </c>
-      <c r="B1" t="str">
-        <v>ruc</v>
-      </c>
-      <c r="C1" t="str">
-        <v>prioridad</v>
-      </c>
-      <c r="D1" t="str">
-        <v>sede</v>
-      </c>
-      <c r="E1" t="str">
-        <v>fecha</v>
-      </c>
-      <c r="F1" t="str">
-        <v>hora_rango</v>
-      </c>
-      <c r="G1" t="str">
-        <v>fecha_programacion</v>
-      </c>
-      <c r="H1" t="str">
-        <v>tipo_operacion</v>
-      </c>
-      <c r="I1" t="str">
-        <v>doc_vigilante</v>
-      </c>
-      <c r="J1" t="str">
-        <v>nro_solicitud</v>
-      </c>
-      <c r="K1" t="str">
-        <v>tipo_arma</v>
-      </c>
-      <c r="L1" t="str">
-        <v>arma</v>
-      </c>
-      <c r="M1" t="str">
-        <v>estado</v>
-      </c>
-      <c r="N1" t="str">
-        <v>observaciones</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id_registro</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ruc</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>prioridad</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>sede</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>hora_rango</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>fecha_programacion</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tipo_operacion</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>doc_vigilante</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>nro_solicitud</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tipo_arma</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>arma</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>estado</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>observaciones</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>J &amp; V Resguardo</v>
-      </c>
-      <c r="C2" t="str">
-        <v>alta</v>
-      </c>
-      <c r="D2" t="str">
-        <v>JEFATURA ZONAL LAMBAYEQUE (EX-INTENDENCIA II NORTE)</v>
-      </c>
-      <c r="E2" t="str">
-        <v>07/04/26</v>
-      </c>
-      <c r="F2" t="str">
-        <v>10:30-10:45</v>
-      </c>
-      <c r="G2" t="str">
-        <v>25/03/2026</v>
-      </c>
-      <c r="H2" t="str">
-        <v>RENOVACIÓN DE LICENCIA DE USO</v>
-      </c>
-      <c r="I2" t="str">
-        <v>77276891</v>
-      </c>
-      <c r="J2" t="str">
-        <v>090086-0</v>
-      </c>
-      <c r="K2" t="str">
-        <v>CORTA</v>
-      </c>
-      <c r="L2" t="str">
-        <v>REVOLVER</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>J &amp; V Resguardo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>JEFATURA ZONAL LAMBAYEQUE (EX-INTENDENCIA II NORTE)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>07/04/26</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>10:30-10:45</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN DE LICENCIA DE USO</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>77276891</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>090086-0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>CORTA</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>REVOLVER</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>No alcanzo cupo para horario 10:30-10:45</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>J &amp; V Resguardo</v>
-      </c>
-      <c r="C3" t="str">
-        <v>normal</v>
-      </c>
-      <c r="D3" t="str">
-        <v>JEFATURA ZONAL DE JUNIN</v>
-      </c>
-      <c r="E3" t="str">
-        <v>31/03/2026</v>
-      </c>
-      <c r="F3" t="str">
-        <v>10:00-10:15</v>
-      </c>
-      <c r="G3" t="str">
-        <v>25/03/2026</v>
-      </c>
-      <c r="H3" t="str">
-        <v>INICIAL DE LICENCIA DE USO</v>
-      </c>
-      <c r="I3" t="str">
-        <v>46724112</v>
-      </c>
-      <c r="J3" t="str">
-        <v>029042-0</v>
-      </c>
-      <c r="K3" t="str">
-        <v>CORTA</v>
-      </c>
-      <c r="L3" t="str">
-        <v>REVOLVER</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>J &amp; V Resguardo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>JEFATURA ZONAL DE JUNIN</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>10:00-10:15</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>INICIAL DE LICENCIA DE USO</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>46724112</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>029042-0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>CORTA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>REVOLVER</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Error en procesamiento: No se encontró Nro Solicitud con token '29042'. Opciones: ['Seleccione']</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>J &amp; V Resguardo</v>
-      </c>
-      <c r="C4" t="str">
-        <v>normal</v>
-      </c>
-      <c r="D4" t="str">
-        <v>JEFATURA ZONAL DE JUNIN</v>
-      </c>
-      <c r="E4" t="str">
-        <v>31/03/2026</v>
-      </c>
-      <c r="F4" t="str">
-        <v>10:00-10:15</v>
-      </c>
-      <c r="G4" t="str">
-        <v>25/03/2026</v>
-      </c>
-      <c r="H4" t="str">
-        <v>INICIAL DE LICENCIA DE USO</v>
-      </c>
-      <c r="I4" t="str">
-        <v>46724112</v>
-      </c>
-      <c r="J4" t="str">
-        <v>029042-0</v>
-      </c>
-      <c r="K4" t="str">
-        <v>LARGA</v>
-      </c>
-      <c r="L4" t="str">
-        <v>ESCOPETA</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>J &amp; V Resguardo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>JEFATURA ZONAL DE JUNIN</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10:00-10:15</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>INICIAL DE LICENCIA DE USO</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>46724112</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>029042-0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>LARGA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>ESCOPETA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Error en procesamiento: No se encontró Nro Solicitud con token '29042'. Opciones: ['Seleccione']</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
-        <v>4</v>
-      </c>
-      <c r="B5" t="str">
-        <v>J &amp; V Resguardo</v>
-      </c>
-      <c r="C5" t="str">
-        <v>normal</v>
-      </c>
-      <c r="D5" t="str">
-        <v>LIMA</v>
-      </c>
-      <c r="E5" t="str">
-        <v>31/03/26</v>
-      </c>
-      <c r="F5" t="str">
-        <v>12:30-12:45</v>
-      </c>
-      <c r="G5" t="str">
-        <v>25/03/2026</v>
-      </c>
-      <c r="H5" t="str">
-        <v>RENOVACIÓN DE LICENCIA DE USO</v>
-      </c>
-      <c r="I5" t="str">
-        <v>44136452</v>
-      </c>
-      <c r="J5" t="str">
-        <v>052340-0</v>
-      </c>
-      <c r="K5" t="str">
-        <v>CORTA</v>
-      </c>
-      <c r="L5" t="str">
-        <v>REVOLVER</v>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>J &amp; V Resguardo</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LIMA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>31/03/26</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>12:30-12:45</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN DE LICENCIA DE USO</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>44136452</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>052340-0</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>CORTA</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>REVOLVER</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>No alcanzo cupo para horario 12:30-12:45</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N5"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/programaciones-armas.xlsx
+++ b/data/programaciones-armas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -640,7 +640,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Error en procesamiento: No se encontró Nro Solicitud con token '29042'. Opciones: ['Seleccione']</t>
+          <t>No se encontró Nro Solicitud/Código de pago para token de 029042-0</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Error en procesamiento: No se encontró Nro Solicitud con token '29042'. Opciones: ['Seleccione']</t>
+          <t>No se encontró Nro Solicitud/Código de pago para token de 029042-0</t>
         </is>
       </c>
     </row>
@@ -785,6 +785,78 @@
       <c r="N5" t="inlineStr">
         <is>
           <t>No alcanzo cupo para horario 12:30-12:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>J &amp; V Resguardo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>JEFATURA ZONAL DE JUNIN</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>31/03/26</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>12:30-12:45</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>25/03/2026</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN DE LICENCIA DE USO</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>76734585</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>052340-0</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>CORTA</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>REVOLVER</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Documento vigilante no disponible para esta razón social/RUC. DNI=76734585 | RUC=J &amp; V Resguardo</t>
         </is>
       </c>
     </row>

--- a/data/programaciones-armas.xlsx
+++ b/data/programaciones-armas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,27 +513,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>alta</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>JEFATURA ZONAL LAMBAYEQUE (EX-INTENDENCIA II NORTE)</t>
+          <t>JEFATURA ZONAL DE ICA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>07/04/26</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10:30-10:45</t>
+          <t>09:00-09:15</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>25/03/2026</t>
+          <t>26/03/2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -543,12 +543,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>77276891</t>
+          <t>22100108</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>090086-0</t>
+          <t>079382-0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -563,300 +563,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Cita Programada</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>No alcanzo cupo para horario 10:30-10:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>J &amp; V Resguardo</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>JEFATURA ZONAL DE JUNIN</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>10:00-10:15</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>25/03/2026</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>INICIAL DE LICENCIA DE USO</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>46724112</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>029042-0</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>CORTA</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>REVOLVER</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>No se encontró Nro Solicitud/Código de pago para token de 029042-0</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>J &amp; V Resguardo</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>JEFATURA ZONAL DE JUNIN</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>10:00-10:15</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>25/03/2026</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>INICIAL DE LICENCIA DE USO</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>46724112</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>029042-0</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>LARGA</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>ESCOPETA</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>No se encontró Nro Solicitud/Código de pago para token de 029042-0</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>J &amp; V Resguardo</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LIMA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>31/03/26</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>12:30-12:45</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>25/03/2026</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>RENOVACIÓN DE LICENCIA DE USO</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>44136452</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>052340-0</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>CORTA</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>REVOLVER</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>No alcanzo cupo para horario 12:30-12:45</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>J &amp; V Resguardo</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>JEFATURA ZONAL DE JUNIN</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>31/03/26</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>12:30-12:45</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>25/03/2026</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>RENOVACIÓN DE LICENCIA DE USO</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>76734585</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>052340-0</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>CORTA</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>REVOLVER</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Pendiente</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Documento vigilante no disponible para esta razón social/RUC. DNI=76734585 | RUC=J &amp; V Resguardo</t>
+          <t>Error no mapeado persistente tras 4 intentos (hora=09:00-09:15, token=079382-0): No se pudo generar cita tras reintentos rápidos</t>
         </is>
       </c>
     </row>

--- a/data/programaciones-armas.xlsx
+++ b/data/programaciones-armas.xlsx
@@ -1,43 +1,58 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <numFmts count="1">
+    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+  </numFmts>
+  <fonts count="1">
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,94 +60,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
 </styleSheet>
 </file>
 
@@ -211,6 +150,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -245,6 +185,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -279,20 +220,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -414,165 +351,224 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:N4"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>id_registro</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ruc</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>prioridad</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>sede</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>fecha</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>hora_rango</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>fecha_programacion</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tipo_operacion</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>doc_vigilante</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>nro_solicitud</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tipo_arma</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>arma</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>estado</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>observaciones</t>
-        </is>
+      <c r="A1" t="str">
+        <v>id_registro</v>
+      </c>
+      <c r="B1" t="str">
+        <v>ruc</v>
+      </c>
+      <c r="C1" t="str">
+        <v>prioridad</v>
+      </c>
+      <c r="D1" t="str">
+        <v>sede</v>
+      </c>
+      <c r="E1" t="str">
+        <v>fecha</v>
+      </c>
+      <c r="F1" t="str">
+        <v>hora_rango</v>
+      </c>
+      <c r="G1" t="str">
+        <v>fecha_programacion</v>
+      </c>
+      <c r="H1" t="str">
+        <v>tipo_operacion</v>
+      </c>
+      <c r="I1" t="str">
+        <v>doc_vigilante</v>
+      </c>
+      <c r="J1" t="str">
+        <v>nro_solicitud</v>
+      </c>
+      <c r="K1" t="str">
+        <v>tipo_arma</v>
+      </c>
+      <c r="L1" t="str">
+        <v>arma</v>
+      </c>
+      <c r="M1" t="str">
+        <v>estado</v>
+      </c>
+      <c r="N1" t="str">
+        <v>observaciones</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>J &amp; V Resguardo</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>JEFATURA ZONAL DE ICA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>09:00-09:15</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>26/03/2026</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>RENOVACIÓN DE LICENCIA DE USO</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>22100108</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>079382-0</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>CORTA</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>REVOLVER</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Cita Programada</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Error no mapeado persistente tras 4 intentos (hora=09:00-09:15, token=079382-0): No se pudo generar cita tras reintentos rápidos</t>
-        </is>
+      <c r="A2" t="str">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>J &amp; V Resguardo</v>
+      </c>
+      <c r="C2" t="str">
+        <v>normal</v>
+      </c>
+      <c r="D2" t="str">
+        <v>JEFATURA ZONAL DE TACNA</v>
+      </c>
+      <c r="E2" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="F2" t="str">
+        <v>12:15-12:30</v>
+      </c>
+      <c r="G2" t="str">
+        <v>27/03/2026</v>
+      </c>
+      <c r="H2" t="str">
+        <v>RENOVACIÓN DE LICENCIA DE USO</v>
+      </c>
+      <c r="I2" t="str">
+        <v>10595436</v>
+      </c>
+      <c r="J2" t="str">
+        <v>052335-0</v>
+      </c>
+      <c r="K2" t="str">
+        <v>CORTA</v>
+      </c>
+      <c r="L2" t="str">
+        <v>PISTOLA</v>
+      </c>
+      <c r="M2" t="str">
+        <v>Pendiente</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>J &amp; V Resguardo</v>
+      </c>
+      <c r="C3" t="str">
+        <v>alta</v>
+      </c>
+      <c r="D3" t="str">
+        <v>JEFATURA ZONAL AREQUIPA (EX-INTENDENCIA III SUR)</v>
+      </c>
+      <c r="E3" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="F3" t="str">
+        <v>11:45-12:00</v>
+      </c>
+      <c r="G3" t="str">
+        <v>27/03/2026</v>
+      </c>
+      <c r="H3" t="str">
+        <v>RENOVACIÓN DE LICENCIA DE USO</v>
+      </c>
+      <c r="I3" t="str">
+        <v>09703265</v>
+      </c>
+      <c r="J3" t="str">
+        <v>075373-0</v>
+      </c>
+      <c r="K3" t="str">
+        <v>CORTA</v>
+      </c>
+      <c r="L3" t="str">
+        <v>PISTOLA</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Pendiente_x000d_</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>J &amp; V Resguardo</v>
+      </c>
+      <c r="C4" t="str">
+        <v>normal</v>
+      </c>
+      <c r="D4" t="str">
+        <v>JEFATURA ZONAL DE LA LIBERTAD</v>
+      </c>
+      <c r="E4" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="F4" t="str">
+        <v>10:30-10:45</v>
+      </c>
+      <c r="G4" t="str">
+        <v>27/03/2026</v>
+      </c>
+      <c r="H4" t="str">
+        <v>INICIAL DE LICENCIA DE USO</v>
+      </c>
+      <c r="I4" t="str">
+        <v>09703265</v>
+      </c>
+      <c r="J4" t="str">
+        <v>049543-0</v>
+      </c>
+      <c r="K4" t="str">
+        <v>CORTA</v>
+      </c>
+      <c r="L4" t="str">
+        <v>PISTOLA</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Pendiente_x000d_</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:N4"/>
+  </ignoredErrors>
 </worksheet>
 </file>
--- a/data/programaciones-armas.xlsx
+++ b/data/programaciones-armas.xlsx
@@ -1,58 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,18 +45,94 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -150,7 +211,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -185,7 +245,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -220,16 +279,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -351,224 +414,309 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>id_registro</v>
-      </c>
-      <c r="B1" t="str">
-        <v>ruc</v>
-      </c>
-      <c r="C1" t="str">
-        <v>prioridad</v>
-      </c>
-      <c r="D1" t="str">
-        <v>sede</v>
-      </c>
-      <c r="E1" t="str">
-        <v>fecha</v>
-      </c>
-      <c r="F1" t="str">
-        <v>hora_rango</v>
-      </c>
-      <c r="G1" t="str">
-        <v>fecha_programacion</v>
-      </c>
-      <c r="H1" t="str">
-        <v>tipo_operacion</v>
-      </c>
-      <c r="I1" t="str">
-        <v>doc_vigilante</v>
-      </c>
-      <c r="J1" t="str">
-        <v>nro_solicitud</v>
-      </c>
-      <c r="K1" t="str">
-        <v>tipo_arma</v>
-      </c>
-      <c r="L1" t="str">
-        <v>arma</v>
-      </c>
-      <c r="M1" t="str">
-        <v>estado</v>
-      </c>
-      <c r="N1" t="str">
-        <v>observaciones</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id_registro</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ruc</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>prioridad</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>sede</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>hora_rango</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>fecha_programacion</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tipo_operacion</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>doc_vigilante</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>nro_solicitud</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tipo_arma</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>arma</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>estado</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>observaciones</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>J &amp; V Resguardo</v>
-      </c>
-      <c r="C2" t="str">
-        <v>normal</v>
-      </c>
-      <c r="D2" t="str">
-        <v>JEFATURA ZONAL DE TACNA</v>
-      </c>
-      <c r="E2" t="str">
-        <v>31/03/2026</v>
-      </c>
-      <c r="F2" t="str">
-        <v>12:15-12:30</v>
-      </c>
-      <c r="G2" t="str">
-        <v>27/03/2026</v>
-      </c>
-      <c r="H2" t="str">
-        <v>RENOVACIÓN DE LICENCIA DE USO</v>
-      </c>
-      <c r="I2" t="str">
-        <v>10595436</v>
-      </c>
-      <c r="J2" t="str">
-        <v>052335-0</v>
-      </c>
-      <c r="K2" t="str">
-        <v>CORTA</v>
-      </c>
-      <c r="L2" t="str">
-        <v>PISTOLA</v>
-      </c>
-      <c r="M2" t="str">
-        <v>Pendiente</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>J &amp; V Resguardo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>JEFATURA ZONAL DE TACNA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>12:15-12:30</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN DE LICENCIA DE USO</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10595436</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>052335-0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>CORTA</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>PISTOLA</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>No se encontró Nro Solicitud/Código de pago para token de 052335-0</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>J &amp; V Resguardo</v>
-      </c>
-      <c r="C3" t="str">
-        <v>alta</v>
-      </c>
-      <c r="D3" t="str">
-        <v>JEFATURA ZONAL AREQUIPA (EX-INTENDENCIA III SUR)</v>
-      </c>
-      <c r="E3" t="str">
-        <v>31/03/2026</v>
-      </c>
-      <c r="F3" t="str">
-        <v>11:45-12:00</v>
-      </c>
-      <c r="G3" t="str">
-        <v>27/03/2026</v>
-      </c>
-      <c r="H3" t="str">
-        <v>RENOVACIÓN DE LICENCIA DE USO</v>
-      </c>
-      <c r="I3" t="str">
-        <v>09703265</v>
-      </c>
-      <c r="J3" t="str">
-        <v>075373-0</v>
-      </c>
-      <c r="K3" t="str">
-        <v>CORTA</v>
-      </c>
-      <c r="L3" t="str">
-        <v>PISTOLA</v>
-      </c>
-      <c r="M3" t="str">
-        <v>Pendiente_x000d_</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>J &amp; V Resguardo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>alta</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>JEFATURA ZONAL AREQUIPA (EX-INTENDENCIA III SUR)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>11:45-12:00</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN DE LICENCIA DE USO</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>09703265</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>075373-0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>CORTA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>PISTOLA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Pendiente_x000d_</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>No alcanzo cupo para horario 11:45-12:00</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>J &amp; V Resguardo</v>
-      </c>
-      <c r="C4" t="str">
-        <v>normal</v>
-      </c>
-      <c r="D4" t="str">
-        <v>JEFATURA ZONAL DE LA LIBERTAD</v>
-      </c>
-      <c r="E4" t="str">
-        <v>09/04/2026</v>
-      </c>
-      <c r="F4" t="str">
-        <v>10:30-10:45</v>
-      </c>
-      <c r="G4" t="str">
-        <v>27/03/2026</v>
-      </c>
-      <c r="H4" t="str">
-        <v>INICIAL DE LICENCIA DE USO</v>
-      </c>
-      <c r="I4" t="str">
-        <v>09703265</v>
-      </c>
-      <c r="J4" t="str">
-        <v>049543-0</v>
-      </c>
-      <c r="K4" t="str">
-        <v>CORTA</v>
-      </c>
-      <c r="L4" t="str">
-        <v>PISTOLA</v>
-      </c>
-      <c r="M4" t="str">
-        <v>Pendiente_x000d_</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>J &amp; V Resguardo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>JEFATURA ZONAL DE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10:30-10:45</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>27/03/2026</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>INICIAL DE LICENCIA DE USO</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>09703265</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>049543-0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>CORTA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>PISTOLA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Pendiente_x000d_</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Error no mapeado persistente tras 4 intentos (hora=10:45-11:00, token=049543-0): No se pudo confirmar la generación de cita de forma robusta (sin seales claras de xito y sin captcha incorrecto explícito)</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N4"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/programaciones-armas.xlsx
+++ b/data/programaciones-armas.xlsx
@@ -533,7 +533,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -605,7 +605,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -677,7 +677,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>27/03/2026</t>
+          <t>30/03/2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>Error no mapeado persistente tras 4 intentos (hora=10:45-11:00, token=049543-0): No se pudo confirmar la generación de cita de forma robusta (sin seales claras de xito y sin captcha incorrecto explícito)</t>
+          <t>No alcanzo cupo para horario 10:30-10:45</t>
         </is>
       </c>
     </row>

--- a/data/programaciones-armas.xlsx
+++ b/data/programaciones-armas.xlsx
@@ -1,58 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr codeName="ThisWorkbook"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
+  <bookViews>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+  </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,18 +45,94 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -150,7 +211,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -185,7 +245,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -220,16 +279,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -351,224 +414,309 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:N4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="str">
-        <v>id_registro</v>
-      </c>
-      <c r="B1" t="str">
-        <v>ruc</v>
-      </c>
-      <c r="C1" t="str">
-        <v>prioridad</v>
-      </c>
-      <c r="D1" t="str">
-        <v>sede</v>
-      </c>
-      <c r="E1" t="str">
-        <v>fecha</v>
-      </c>
-      <c r="F1" t="str">
-        <v>hora_rango</v>
-      </c>
-      <c r="G1" t="str">
-        <v>fecha_programacion</v>
-      </c>
-      <c r="H1" t="str">
-        <v>tipo_operacion</v>
-      </c>
-      <c r="I1" t="str">
-        <v>doc_vigilante</v>
-      </c>
-      <c r="J1" t="str">
-        <v>nro_solicitud</v>
-      </c>
-      <c r="K1" t="str">
-        <v>tipo_arma</v>
-      </c>
-      <c r="L1" t="str">
-        <v>arma</v>
-      </c>
-      <c r="M1" t="str">
-        <v>estado</v>
-      </c>
-      <c r="N1" t="str">
-        <v>observaciones</v>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>id_registro</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>ruc</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>prioridad</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>sede</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>fecha</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>hora_rango</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>fecha_programacion</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tipo_operacion</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>doc_vigilante</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>nro_solicitud</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tipo_arma</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>arma</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>estado</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>observaciones</t>
+        </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>1</v>
-      </c>
-      <c r="B2" t="str">
-        <v>J &amp; V Resguardo</v>
-      </c>
-      <c r="C2" t="str">
-        <v>normal</v>
-      </c>
-      <c r="D2" t="str">
-        <v>JEFATURA ZONAL DE TACNA</v>
-      </c>
-      <c r="E2" t="str">
-        <v>31/03/2026</v>
-      </c>
-      <c r="F2" t="str">
-        <v>12:15-12:30</v>
-      </c>
-      <c r="G2" t="str">
-        <v>30/03/2026</v>
-      </c>
-      <c r="H2" t="str">
-        <v>RENOVACIÓN DE LICENCIA DE USO</v>
-      </c>
-      <c r="I2" t="str">
-        <v>10595436</v>
-      </c>
-      <c r="J2" t="str">
-        <v>052335-0</v>
-      </c>
-      <c r="K2" t="str">
-        <v>CORTA</v>
-      </c>
-      <c r="L2" t="str">
-        <v>PISTOLA</v>
-      </c>
-      <c r="M2" t="str">
-        <v>Pendiente</v>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>J &amp; V Resguardo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>JEFATURA ZONAL DE TACNA</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>12:15-12:30</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN DE LICENCIA DE USO</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10595436</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>052335-0</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>CORTA</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>PISTOLA</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>No se encontró Nro Solicitud/Código de pago para token de 052335-0</t>
+        </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>J &amp; V Resguardo</v>
-      </c>
-      <c r="C3" t="str">
-        <v>alta</v>
-      </c>
-      <c r="D3" t="str">
-        <v>JEFATURA ZONAL AREQUIPA (EX-INTENDENCIA III SUR)</v>
-      </c>
-      <c r="E3" t="str">
-        <v>31/03/2026</v>
-      </c>
-      <c r="F3" t="str">
-        <v>11:45-12:00</v>
-      </c>
-      <c r="G3" t="str">
-        <v>30/03/2026</v>
-      </c>
-      <c r="H3" t="str">
-        <v>RENOVACIÓN DE LICENCIA DE USO</v>
-      </c>
-      <c r="I3" t="str">
-        <v>09703265</v>
-      </c>
-      <c r="J3" t="str">
-        <v>075373-0</v>
-      </c>
-      <c r="K3" t="str">
-        <v>CORTA</v>
-      </c>
-      <c r="L3" t="str">
-        <v>PISTOLA</v>
-      </c>
-      <c r="M3" t="str">
-        <v>Pendiente_x000d_</v>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>J &amp; V Resguardo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>JEFATURA ZONAL DE LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>09:30-09:45</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>INICIAL DE LICENCIA DE USO</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>09703265</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>049543-0</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>CORTA</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>PISTOLA</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Pendiente_x000d_</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Ya existe un turno registrado para la misma persona y Tipo de Licencia. DNI=09703265 | TipoOperacion=INICIAL DE LICENCIA DE USO</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>J &amp; V Resguardo</v>
-      </c>
-      <c r="C4" t="str">
-        <v>normal</v>
-      </c>
-      <c r="D4" t="str">
-        <v>JEFATURA ZONAL DE LA LIBERTAD</v>
-      </c>
-      <c r="E4" t="str">
-        <v>09/04/2026</v>
-      </c>
-      <c r="F4" t="str">
-        <v>10:30-10:45</v>
-      </c>
-      <c r="G4" t="str">
-        <v>30/03/2026</v>
-      </c>
-      <c r="H4" t="str">
-        <v>INICIAL DE LICENCIA DE USO</v>
-      </c>
-      <c r="I4" t="str">
-        <v>09703265</v>
-      </c>
-      <c r="J4" t="str">
-        <v>049543-0</v>
-      </c>
-      <c r="K4" t="str">
-        <v>CORTA</v>
-      </c>
-      <c r="L4" t="str">
-        <v>PISTOLA</v>
-      </c>
-      <c r="M4" t="str">
-        <v>Pendiente_x000d_</v>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>J &amp; V Resguardo</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>normal</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>JEFATURA ZONAL AREQUIPA (EX-INTENDENCIA III SUR)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>11:45-12:00</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>30/03/2026</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>RENOVACIÓN DE LICENCIA DE USO</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>09703265</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>075373-0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>CORTA</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>PISTOLA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Pendiente_x000d_</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>No alcanzo cupo para horario 11:45-12:00</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N4"/>
-  </ignoredErrors>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/programaciones-armas.xlsx
+++ b/data/programaciones-armas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -566,9 +566,91 @@
         <v>Pendiente_x000d_</v>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>J &amp; V Resguardo</v>
+      </c>
+      <c r="C5" t="str">
+        <v>normal</v>
+      </c>
+      <c r="D5" t="str">
+        <v>JEFATURA ZONAL DE CAJAMARCA</v>
+      </c>
+      <c r="E5" t="str">
+        <v>31/03/2026</v>
+      </c>
+      <c r="F5" t="str">
+        <v>12:00-12:15</v>
+      </c>
+      <c r="G5" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="H5" t="str">
+        <v>RENOVACIÓN DE LICENCIA DE USO</v>
+      </c>
+      <c r="I5" t="str">
+        <v>09703265</v>
+      </c>
+      <c r="J5" t="str">
+        <v>038324-0</v>
+      </c>
+      <c r="K5" t="str">
+        <v>CORTA</v>
+      </c>
+      <c r="L5" t="str">
+        <v>PISTOLA</v>
+      </c>
+      <c r="M5" t="str">
+        <v>Pendiente_x000d_</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>J &amp; V Resguardo</v>
+      </c>
+      <c r="C6" t="str">
+        <v>normal</v>
+      </c>
+      <c r="D6" t="str">
+        <v>JEFATURA ZONAL DE LA LIBERTAD</v>
+      </c>
+      <c r="E6" t="str">
+        <v>09/04/2026</v>
+      </c>
+      <c r="F6" t="str">
+        <v>09:45-10:00</v>
+      </c>
+      <c r="G6" t="str">
+        <v>30/03/2026</v>
+      </c>
+      <c r="H6" t="str">
+        <v>INICIAL DE LICENCIA DE USO</v>
+      </c>
+      <c r="I6" t="str">
+        <v>09703267</v>
+      </c>
+      <c r="J6" t="str">
+        <v>049543-0</v>
+      </c>
+      <c r="K6" t="str">
+        <v>CORTA</v>
+      </c>
+      <c r="L6" t="str">
+        <v>PISTOLA</v>
+      </c>
+      <c r="M6" t="str">
+        <v>Pendiente_x000d_</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/programaciones-armas.xlsx
+++ b/data/programaciones-armas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -454,31 +454,31 @@
         <v>normal</v>
       </c>
       <c r="D2" t="str">
-        <v>JEFATURA ZONAL DE LA LIBERTAD</v>
+        <v>LIMA</v>
       </c>
       <c r="E2" t="str">
-        <v>09/04/2026</v>
+        <v>21/04/2026</v>
       </c>
       <c r="F2" t="str">
-        <v>09:45-10:00</v>
+        <v>08:30-08:45</v>
       </c>
       <c r="G2" t="str">
-        <v>30/03/2026</v>
+        <v>31/03/2026</v>
       </c>
       <c r="H2" t="str">
         <v>INICIAL DE LICENCIA DE USO</v>
       </c>
       <c r="I2" t="str">
-        <v>09703265</v>
+        <v>77095597</v>
       </c>
       <c r="J2" t="str">
-        <v>049543-0</v>
+        <v>043788-0</v>
       </c>
       <c r="K2" t="str">
         <v>CORTA</v>
       </c>
       <c r="L2" t="str">
-        <v>PISTOLA</v>
+        <v>REVOLVER</v>
       </c>
       <c r="M2" t="str">
         <v>Pendiente_x000d_</v>
@@ -495,25 +495,25 @@
         <v>normal</v>
       </c>
       <c r="D3" t="str">
-        <v>JEFATURA ZONAL DE TACNA</v>
+        <v>LIMA</v>
       </c>
       <c r="E3" t="str">
+        <v>21/04/2026</v>
+      </c>
+      <c r="F3" t="str">
+        <v>09:00-09:15</v>
+      </c>
+      <c r="G3" t="str">
         <v>31/03/2026</v>
-      </c>
-      <c r="F3" t="str">
-        <v>12:15-12:30</v>
-      </c>
-      <c r="G3" t="str">
-        <v>30/03/2026</v>
       </c>
       <c r="H3" t="str">
         <v>RENOVACIÓN DE LICENCIA DE USO</v>
       </c>
       <c r="I3" t="str">
-        <v>10595436</v>
+        <v>08666044</v>
       </c>
       <c r="J3" t="str">
-        <v>052335-0</v>
+        <v>043503-0</v>
       </c>
       <c r="K3" t="str">
         <v>CORTA</v>
@@ -536,25 +536,25 @@
         <v>normal</v>
       </c>
       <c r="D4" t="str">
-        <v>JEFATURA ZONAL AREQUIPA (EX-INTENDENCIA III SUR)</v>
+        <v>LIMA</v>
       </c>
       <c r="E4" t="str">
+        <v>21/04/2026</v>
+      </c>
+      <c r="F4" t="str">
+        <v>09:00-09:15</v>
+      </c>
+      <c r="G4" t="str">
         <v>31/03/2026</v>
-      </c>
-      <c r="F4" t="str">
-        <v>08:45-09:00</v>
-      </c>
-      <c r="G4" t="str">
-        <v>30/03/2026</v>
       </c>
       <c r="H4" t="str">
         <v>RENOVACIÓN DE LICENCIA DE USO</v>
       </c>
       <c r="I4" t="str">
-        <v>09703265</v>
+        <v>15740016</v>
       </c>
       <c r="J4" t="str">
-        <v>075373-0</v>
+        <v>043504-0</v>
       </c>
       <c r="K4" t="str">
         <v>CORTA</v>
@@ -568,89 +568,12 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>4</v>
-      </c>
-      <c r="B5" t="str">
-        <v>J &amp; V Resguardo</v>
-      </c>
-      <c r="C5" t="str">
-        <v>normal</v>
-      </c>
-      <c r="D5" t="str">
-        <v>JEFATURA ZONAL DE CAJAMARCA</v>
-      </c>
-      <c r="E5" t="str">
-        <v>31/03/2026</v>
-      </c>
-      <c r="F5" t="str">
-        <v>12:00-12:15</v>
-      </c>
-      <c r="G5" t="str">
-        <v>30/03/2026</v>
-      </c>
-      <c r="H5" t="str">
-        <v>RENOVACIÓN DE LICENCIA DE USO</v>
-      </c>
-      <c r="I5" t="str">
-        <v>09703265</v>
-      </c>
-      <c r="J5" t="str">
-        <v>038324-0</v>
-      </c>
-      <c r="K5" t="str">
-        <v>CORTA</v>
-      </c>
-      <c r="L5" t="str">
-        <v>PISTOLA</v>
-      </c>
-      <c r="M5" t="str">
-        <v>Pendiente_x000d_</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>5</v>
-      </c>
-      <c r="B6" t="str">
-        <v>J &amp; V Resguardo</v>
-      </c>
-      <c r="C6" t="str">
-        <v>normal</v>
-      </c>
-      <c r="D6" t="str">
-        <v>JEFATURA ZONAL DE LA LIBERTAD</v>
-      </c>
-      <c r="E6" t="str">
-        <v>09/04/2026</v>
-      </c>
-      <c r="F6" t="str">
-        <v>09:45-10:00</v>
-      </c>
-      <c r="G6" t="str">
-        <v>30/03/2026</v>
-      </c>
-      <c r="H6" t="str">
-        <v>INICIAL DE LICENCIA DE USO</v>
-      </c>
-      <c r="I6" t="str">
-        <v>09703267</v>
-      </c>
-      <c r="J6" t="str">
-        <v>049543-0</v>
-      </c>
-      <c r="K6" t="str">
-        <v>CORTA</v>
-      </c>
-      <c r="L6" t="str">
-        <v>PISTOLA</v>
-      </c>
-      <c r="M6" t="str">
-        <v>Pendiente_x000d_</v>
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/programaciones-armas.xlsx
+++ b/data/programaciones-armas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N5"/>
+  <dimension ref="A1:N6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -451,28 +451,28 @@
         <v>J &amp; V Resguardo</v>
       </c>
       <c r="C2" t="str">
-        <v>normal</v>
+        <v>alta</v>
       </c>
       <c r="D2" t="str">
         <v>LIMA</v>
       </c>
       <c r="E2" t="str">
-        <v>21/04/2026</v>
+        <v>22/04/2026</v>
       </c>
       <c r="F2" t="str">
-        <v>08:30-08:45</v>
+        <v>08:00-08:15</v>
       </c>
       <c r="G2" t="str">
-        <v>31/03/2026</v>
+        <v>1/04/2026</v>
       </c>
       <c r="H2" t="str">
         <v>INICIAL DE LICENCIA DE USO</v>
       </c>
       <c r="I2" t="str">
-        <v>77095597</v>
+        <v>09452250</v>
       </c>
       <c r="J2" t="str">
-        <v>043788-0</v>
+        <v>080000-0</v>
       </c>
       <c r="K2" t="str">
         <v>CORTA</v>
@@ -492,28 +492,28 @@
         <v>J &amp; V Resguardo</v>
       </c>
       <c r="C3" t="str">
-        <v>normal</v>
+        <v>alta</v>
       </c>
       <c r="D3" t="str">
         <v>LIMA</v>
       </c>
       <c r="E3" t="str">
-        <v>21/04/2026</v>
+        <v>22/04/2026</v>
       </c>
       <c r="F3" t="str">
         <v>09:00-09:15</v>
       </c>
       <c r="G3" t="str">
-        <v>31/03/2026</v>
+        <v>1/04/2026</v>
       </c>
       <c r="H3" t="str">
         <v>RENOVACIÓN DE LICENCIA DE USO</v>
       </c>
       <c r="I3" t="str">
-        <v>08666044</v>
+        <v>43440164</v>
       </c>
       <c r="J3" t="str">
-        <v>043503-0</v>
+        <v>068399-0</v>
       </c>
       <c r="K3" t="str">
         <v>CORTA</v>
@@ -539,28 +539,28 @@
         <v>LIMA</v>
       </c>
       <c r="E4" t="str">
-        <v>21/04/2026</v>
+        <v>22/04/2026</v>
       </c>
       <c r="F4" t="str">
-        <v>09:00-09:15</v>
+        <v>08:00-08:15</v>
       </c>
       <c r="G4" t="str">
-        <v>31/03/2026</v>
+        <v>1/04/2026</v>
       </c>
       <c r="H4" t="str">
         <v>RENOVACIÓN DE LICENCIA DE USO</v>
       </c>
       <c r="I4" t="str">
-        <v>15740016</v>
+        <v>60274318</v>
       </c>
       <c r="J4" t="str">
-        <v>043504-0</v>
+        <v>094587-0</v>
       </c>
       <c r="K4" t="str">
         <v>CORTA</v>
       </c>
       <c r="L4" t="str">
-        <v>PISTOLA</v>
+        <v>REVOLVER</v>
       </c>
       <c r="M4" t="str">
         <v>Pendiente_x000d_</v>
@@ -568,12 +568,53 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>J &amp; V Resguardo</v>
+      </c>
+      <c r="C5" t="str">
+        <v>normal</v>
+      </c>
+      <c r="D5" t="str">
+        <v>LIMA</v>
+      </c>
+      <c r="E5" t="str">
+        <v>22/04/2026</v>
+      </c>
+      <c r="F5" t="str">
+        <v>09:00-09:15</v>
+      </c>
+      <c r="G5" t="str">
+        <v>1/04/2026</v>
+      </c>
+      <c r="H5" t="str">
+        <v>RENOVACIÓN DE LICENCIA DE USO</v>
+      </c>
+      <c r="I5" t="str">
+        <v>75151780</v>
+      </c>
+      <c r="J5" t="str">
+        <v>052332-0</v>
+      </c>
+      <c r="K5" t="str">
+        <v>CORTA</v>
+      </c>
+      <c r="L5" t="str">
+        <v>REVOLVER</v>
+      </c>
+      <c r="M5" t="str">
+        <v>Pendiente_x000d_</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/programaciones-armas.xlsx
+++ b/data/programaciones-armas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:N7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -457,22 +457,22 @@
         <v>LIMA</v>
       </c>
       <c r="E2" t="str">
-        <v>22/04/2026</v>
+        <v>7/05/2026</v>
       </c>
       <c r="F2" t="str">
-        <v>08:00-08:15</v>
+        <v>12:00-12:15</v>
       </c>
       <c r="G2" t="str">
-        <v>1/04/2026</v>
+        <v>16/04/2026</v>
       </c>
       <c r="H2" t="str">
-        <v>INICIAL DE LICENCIA DE USO</v>
+        <v>RENOVACION DE LICENCIA DE USO</v>
       </c>
       <c r="I2" t="str">
-        <v>09452250</v>
+        <v>45429407</v>
       </c>
       <c r="J2" t="str">
-        <v>080000-0</v>
+        <v>098411-0</v>
       </c>
       <c r="K2" t="str">
         <v>CORTA</v>
@@ -498,123 +498,41 @@
         <v>LIMA</v>
       </c>
       <c r="E3" t="str">
-        <v>22/04/2026</v>
+        <v>7/05/2026</v>
       </c>
       <c r="F3" t="str">
-        <v>09:00-09:15</v>
+        <v>12:15-12:30</v>
       </c>
       <c r="G3" t="str">
-        <v>1/04/2026</v>
+        <v>16/04/2026</v>
       </c>
       <c r="H3" t="str">
-        <v>RENOVACIÓN DE LICENCIA DE USO</v>
+        <v>INICIAL DE LICENCIA DE USO</v>
       </c>
       <c r="I3" t="str">
-        <v>43440164</v>
+        <v>10212773</v>
       </c>
       <c r="J3" t="str">
-        <v>068399-0</v>
+        <v>071549-0</v>
       </c>
       <c r="K3" t="str">
         <v>CORTA</v>
       </c>
       <c r="L3" t="str">
-        <v>PISTOLA</v>
+        <v>REVOLVER</v>
       </c>
       <c r="M3" t="str">
         <v>Pendiente_x000d_</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>J &amp; V Resguardo</v>
-      </c>
-      <c r="C4" t="str">
-        <v>normal</v>
-      </c>
-      <c r="D4" t="str">
-        <v>LIMA</v>
-      </c>
-      <c r="E4" t="str">
-        <v>22/04/2026</v>
-      </c>
-      <c r="F4" t="str">
-        <v>08:00-08:15</v>
-      </c>
-      <c r="G4" t="str">
-        <v>1/04/2026</v>
-      </c>
-      <c r="H4" t="str">
-        <v>RENOVACIÓN DE LICENCIA DE USO</v>
-      </c>
-      <c r="I4" t="str">
-        <v>60274318</v>
-      </c>
-      <c r="J4" t="str">
-        <v>094587-0</v>
-      </c>
-      <c r="K4" t="str">
-        <v>CORTA</v>
-      </c>
-      <c r="L4" t="str">
-        <v>REVOLVER</v>
-      </c>
-      <c r="M4" t="str">
-        <v>Pendiente_x000d_</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>4</v>
-      </c>
-      <c r="B5" t="str">
-        <v>J &amp; V Resguardo</v>
-      </c>
-      <c r="C5" t="str">
-        <v>normal</v>
-      </c>
-      <c r="D5" t="str">
-        <v>LIMA</v>
-      </c>
-      <c r="E5" t="str">
-        <v>22/04/2026</v>
-      </c>
-      <c r="F5" t="str">
-        <v>09:00-09:15</v>
-      </c>
-      <c r="G5" t="str">
-        <v>1/04/2026</v>
-      </c>
-      <c r="H5" t="str">
-        <v>RENOVACIÓN DE LICENCIA DE USO</v>
-      </c>
-      <c r="I5" t="str">
-        <v>75151780</v>
-      </c>
-      <c r="J5" t="str">
-        <v>052332-0</v>
-      </c>
-      <c r="K5" t="str">
-        <v>CORTA</v>
-      </c>
-      <c r="L5" t="str">
-        <v>REVOLVER</v>
-      </c>
-      <c r="M5" t="str">
-        <v>Pendiente_x000d_</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
+    <row r="7">
+      <c r="A7" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/programaciones-armas.xlsx
+++ b/data/programaciones-armas.xlsx
@@ -457,22 +457,22 @@
         <v>LIMA</v>
       </c>
       <c r="E2" t="str">
-        <v>7/05/2026</v>
+        <v>8/05/2026</v>
       </c>
       <c r="F2" t="str">
         <v>12:00-12:15</v>
       </c>
       <c r="G2" t="str">
-        <v>16/04/2026</v>
+        <v>17/04/2026</v>
       </c>
       <c r="H2" t="str">
-        <v>RENOVACION DE LICENCIA DE USO</v>
+        <v>INICIAL DE LICENCIA DE USO</v>
       </c>
       <c r="I2" t="str">
-        <v>45429407</v>
+        <v>76023039</v>
       </c>
       <c r="J2" t="str">
-        <v>098411-0</v>
+        <v>043793-0</v>
       </c>
       <c r="K2" t="str">
         <v>CORTA</v>
@@ -498,22 +498,22 @@
         <v>LIMA</v>
       </c>
       <c r="E3" t="str">
-        <v>7/05/2026</v>
+        <v>8/05/2026</v>
       </c>
       <c r="F3" t="str">
-        <v>12:15-12:30</v>
+        <v>12:00-12:15</v>
       </c>
       <c r="G3" t="str">
-        <v>16/04/2026</v>
+        <v>17/04/2026</v>
       </c>
       <c r="H3" t="str">
-        <v>INICIAL DE LICENCIA DE USO</v>
+        <v>RENOVACION DE LICENCIA DE USO</v>
       </c>
       <c r="I3" t="str">
-        <v>10212773</v>
+        <v>00966547</v>
       </c>
       <c r="J3" t="str">
-        <v>071549-0</v>
+        <v>098412-0</v>
       </c>
       <c r="K3" t="str">
         <v>CORTA</v>
@@ -523,6 +523,52 @@
       </c>
       <c r="M3" t="str">
         <v>Pendiente_x000d_</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>J &amp; V Resguardo</v>
+      </c>
+      <c r="C4" t="str">
+        <v>alta</v>
+      </c>
+      <c r="D4" t="str">
+        <v>LIMA</v>
+      </c>
+      <c r="E4" t="str">
+        <v>8/05/2026</v>
+      </c>
+      <c r="F4" t="str">
+        <v>11:45-12:00</v>
+      </c>
+      <c r="G4" t="str">
+        <v>17/04/2026</v>
+      </c>
+      <c r="H4" t="str">
+        <v>RENOVACION DE LICENCIA DE USO</v>
+      </c>
+      <c r="I4" t="str">
+        <v>45759844</v>
+      </c>
+      <c r="J4" t="str">
+        <v>085709-0</v>
+      </c>
+      <c r="K4" t="str">
+        <v>CORTA</v>
+      </c>
+      <c r="L4" t="str">
+        <v>PISTOLA</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Pendiente_x000d_</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
       </c>
     </row>
     <row r="7">

--- a/data/programaciones-armas.xlsx
+++ b/data/programaciones-armas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:N8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -457,13 +457,13 @@
         <v>LIMA</v>
       </c>
       <c r="E2" t="str">
-        <v>8/05/2026</v>
+        <v>15/05/2026</v>
       </c>
       <c r="F2" t="str">
         <v>12:00-12:15</v>
       </c>
       <c r="G2" t="str">
-        <v>17/04/2026</v>
+        <v>24/04/2026</v>
       </c>
       <c r="H2" t="str">
         <v>INICIAL DE LICENCIA DE USO</v>
@@ -498,22 +498,22 @@
         <v>LIMA</v>
       </c>
       <c r="E3" t="str">
-        <v>8/05/2026</v>
+        <v>15/05/2026</v>
       </c>
       <c r="F3" t="str">
         <v>12:00-12:15</v>
       </c>
       <c r="G3" t="str">
-        <v>17/04/2026</v>
+        <v>24/04/2026</v>
       </c>
       <c r="H3" t="str">
-        <v>RENOVACION DE LICENCIA DE USO</v>
+        <v>RENOVACIÓN DE LICENCIA DE USO</v>
       </c>
       <c r="I3" t="str">
-        <v>00966547</v>
+        <v>47694399</v>
       </c>
       <c r="J3" t="str">
-        <v>098412-0</v>
+        <v>099008-0</v>
       </c>
       <c r="K3" t="str">
         <v>CORTA</v>
@@ -527,47 +527,6 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>3</v>
-      </c>
-      <c r="B4" t="str">
-        <v>J &amp; V Resguardo</v>
-      </c>
-      <c r="C4" t="str">
-        <v>alta</v>
-      </c>
-      <c r="D4" t="str">
-        <v>LIMA</v>
-      </c>
-      <c r="E4" t="str">
-        <v>8/05/2026</v>
-      </c>
-      <c r="F4" t="str">
-        <v>11:45-12:00</v>
-      </c>
-      <c r="G4" t="str">
-        <v>17/04/2026</v>
-      </c>
-      <c r="H4" t="str">
-        <v>RENOVACION DE LICENCIA DE USO</v>
-      </c>
-      <c r="I4" t="str">
-        <v>45759844</v>
-      </c>
-      <c r="J4" t="str">
-        <v>085709-0</v>
-      </c>
-      <c r="K4" t="str">
-        <v>CORTA</v>
-      </c>
-      <c r="L4" t="str">
-        <v>PISTOLA</v>
-      </c>
-      <c r="M4" t="str">
-        <v>Pendiente_x000d_</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
         <v/>
       </c>
     </row>
@@ -576,9 +535,14 @@
         <v/>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/programaciones-armas.xlsx
+++ b/data/programaciones-armas.xlsx
@@ -454,25 +454,25 @@
         <v>alta</v>
       </c>
       <c r="D2" t="str">
-        <v>LIMA</v>
+        <v>JEFATURA ZONAL DE ICA</v>
       </c>
       <c r="E2" t="str">
-        <v>15/05/2026</v>
+        <v>30/04/2026</v>
       </c>
       <c r="F2" t="str">
-        <v>12:00-12:15</v>
+        <v>10:00-10:15</v>
       </c>
       <c r="G2" t="str">
         <v>24/04/2026</v>
       </c>
       <c r="H2" t="str">
-        <v>INICIAL DE LICENCIA DE USO</v>
+        <v>RENOVACION DE LICENCIA DE USO</v>
       </c>
       <c r="I2" t="str">
-        <v>76023039</v>
+        <v>60389562</v>
       </c>
       <c r="J2" t="str">
-        <v>043793-0</v>
+        <v>085704-0</v>
       </c>
       <c r="K2" t="str">
         <v>CORTA</v>
@@ -481,47 +481,6 @@
         <v>REVOLVER</v>
       </c>
       <c r="M2" t="str">
-        <v>Pendiente_x000d_</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>2</v>
-      </c>
-      <c r="B3" t="str">
-        <v>J &amp; V Resguardo</v>
-      </c>
-      <c r="C3" t="str">
-        <v>alta</v>
-      </c>
-      <c r="D3" t="str">
-        <v>LIMA</v>
-      </c>
-      <c r="E3" t="str">
-        <v>15/05/2026</v>
-      </c>
-      <c r="F3" t="str">
-        <v>12:00-12:15</v>
-      </c>
-      <c r="G3" t="str">
-        <v>24/04/2026</v>
-      </c>
-      <c r="H3" t="str">
-        <v>RENOVACIÓN DE LICENCIA DE USO</v>
-      </c>
-      <c r="I3" t="str">
-        <v>47694399</v>
-      </c>
-      <c r="J3" t="str">
-        <v>099008-0</v>
-      </c>
-      <c r="K3" t="str">
-        <v>CORTA</v>
-      </c>
-      <c r="L3" t="str">
-        <v>REVOLVER</v>
-      </c>
-      <c r="M3" t="str">
         <v>Pendiente_x000d_</v>
       </c>
     </row>

--- a/data/programaciones-armas.xlsx
+++ b/data/programaciones-armas.xlsx
@@ -454,25 +454,25 @@
         <v>alta</v>
       </c>
       <c r="D2" t="str">
-        <v>JEFATURA ZONAL DE ICA</v>
+        <v>LIMA</v>
       </c>
       <c r="E2" t="str">
-        <v>30/04/2026</v>
+        <v>19/05/2026</v>
       </c>
       <c r="F2" t="str">
-        <v>10:00-10:15</v>
+        <v>12:00-12:15</v>
       </c>
       <c r="G2" t="str">
-        <v>24/04/2026</v>
+        <v>28/04/2026</v>
       </c>
       <c r="H2" t="str">
         <v>RENOVACION DE LICENCIA DE USO</v>
       </c>
       <c r="I2" t="str">
-        <v>60389562</v>
+        <v>40598949</v>
       </c>
       <c r="J2" t="str">
-        <v>085704-0</v>
+        <v>052333-0</v>
       </c>
       <c r="K2" t="str">
         <v>CORTA</v>
@@ -481,6 +481,47 @@
         <v>REVOLVER</v>
       </c>
       <c r="M2" t="str">
+        <v>Pendiente_x000d_</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>J &amp; V Resguardo</v>
+      </c>
+      <c r="C3" t="str">
+        <v>alta</v>
+      </c>
+      <c r="D3" t="str">
+        <v>LIMA</v>
+      </c>
+      <c r="E3" t="str">
+        <v>19/05/2026</v>
+      </c>
+      <c r="F3" t="str">
+        <v>12:00-12:15</v>
+      </c>
+      <c r="G3" t="str">
+        <v>28/04/2026</v>
+      </c>
+      <c r="H3" t="str">
+        <v>RENOVACION DE LICENCIA DE USO</v>
+      </c>
+      <c r="I3" t="str">
+        <v>73799884</v>
+      </c>
+      <c r="J3" t="str">
+        <v>037411-0</v>
+      </c>
+      <c r="K3" t="str">
+        <v>CORTA</v>
+      </c>
+      <c r="L3" t="str">
+        <v>REVOLVER</v>
+      </c>
+      <c r="M3" t="str">
         <v>Pendiente_x000d_</v>
       </c>
     </row>

--- a/data/programaciones-armas.xlsx
+++ b/data/programaciones-armas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N10"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -457,28 +457,28 @@
         <v>LIMA</v>
       </c>
       <c r="E2" t="str">
-        <v>19/05/2026</v>
+        <v>29/05/2026</v>
       </c>
       <c r="F2" t="str">
-        <v>12:00-12:15</v>
+        <v>08:00-08:15</v>
       </c>
       <c r="G2" t="str">
-        <v>28/04/2026</v>
+        <v>8/05/2026</v>
       </c>
       <c r="H2" t="str">
         <v>RENOVACION DE LICENCIA DE USO</v>
       </c>
       <c r="I2" t="str">
-        <v>40598949</v>
+        <v>09627091</v>
       </c>
       <c r="J2" t="str">
-        <v>052333-0</v>
+        <v>060579-0</v>
       </c>
       <c r="K2" t="str">
         <v>CORTA</v>
       </c>
       <c r="L2" t="str">
-        <v>REVOLVER</v>
+        <v>PISTOLA</v>
       </c>
       <c r="M2" t="str">
         <v>Pendiente_x000d_</v>
@@ -498,28 +498,28 @@
         <v>LIMA</v>
       </c>
       <c r="E3" t="str">
-        <v>19/05/2026</v>
+        <v>29/05/2026</v>
       </c>
       <c r="F3" t="str">
-        <v>12:00-12:15</v>
+        <v>08:15-08:30</v>
       </c>
       <c r="G3" t="str">
-        <v>28/04/2026</v>
+        <v>8/05/2026</v>
       </c>
       <c r="H3" t="str">
         <v>RENOVACION DE LICENCIA DE USO</v>
       </c>
       <c r="I3" t="str">
-        <v>73799884</v>
+        <v>10198664</v>
       </c>
       <c r="J3" t="str">
-        <v>037411-0</v>
+        <v>020858-0</v>
       </c>
       <c r="K3" t="str">
         <v>CORTA</v>
       </c>
       <c r="L3" t="str">
-        <v>REVOLVER</v>
+        <v>PISTOLA</v>
       </c>
       <c r="M3" t="str">
         <v>Pendiente_x000d_</v>
@@ -527,22 +527,258 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v/>
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>J &amp; V Resguardo</v>
+      </c>
+      <c r="C4" t="str">
+        <v>alta</v>
+      </c>
+      <c r="D4" t="str">
+        <v>LIMA</v>
+      </c>
+      <c r="E4" t="str">
+        <v>29/05/2026</v>
+      </c>
+      <c r="F4" t="str">
+        <v>09:00-09:15</v>
+      </c>
+      <c r="G4" t="str">
+        <v>8/05/2026</v>
+      </c>
+      <c r="H4" t="str">
+        <v>RENOVACION DE LICENCIA DE USO</v>
+      </c>
+      <c r="I4" t="str">
+        <v>10439677</v>
+      </c>
+      <c r="J4" t="str">
+        <v>099009-0</v>
+      </c>
+      <c r="K4" t="str">
+        <v>CORTA</v>
+      </c>
+      <c r="L4" t="str">
+        <v>REVOLVER</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Pendiente_x000d_</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>J &amp; V Resguardo</v>
+      </c>
+      <c r="C5" t="str">
+        <v>alta</v>
+      </c>
+      <c r="D5" t="str">
+        <v>LIMA</v>
+      </c>
+      <c r="E5" t="str">
+        <v>29/05/2026</v>
+      </c>
+      <c r="F5" t="str">
+        <v>11:15-11:30</v>
+      </c>
+      <c r="G5" t="str">
+        <v>8/05/2026</v>
+      </c>
+      <c r="H5" t="str">
+        <v>INICIAL DE LICENCIA DE USO</v>
+      </c>
+      <c r="I5" t="str">
+        <v>78997430</v>
+      </c>
+      <c r="J5" t="str">
+        <v>100403-0</v>
+      </c>
+      <c r="K5" t="str">
+        <v>CORTA</v>
+      </c>
+      <c r="L5" t="str">
+        <v>REVOLVER</v>
+      </c>
+      <c r="M5" t="str">
+        <v>Pendiente_x000d_</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>5</v>
+      </c>
+      <c r="B6" t="str">
+        <v>J &amp; V Resguardo</v>
+      </c>
+      <c r="C6" t="str">
+        <v>alta</v>
+      </c>
+      <c r="D6" t="str">
+        <v>LIMA</v>
+      </c>
+      <c r="E6" t="str">
+        <v>29/05/2026</v>
+      </c>
+      <c r="F6" t="str">
+        <v>11:15-11:30</v>
+      </c>
+      <c r="G6" t="str">
+        <v>8/05/2026</v>
+      </c>
+      <c r="H6" t="str">
+        <v>INICIAL DE LICENCIA DE USO</v>
+      </c>
+      <c r="I6" t="str">
+        <v>78997430</v>
+      </c>
+      <c r="J6" t="str">
+        <v>100403-0</v>
+      </c>
+      <c r="K6" t="str">
+        <v>LARGA</v>
+      </c>
+      <c r="L6" t="str">
+        <v>ESCOPETA</v>
+      </c>
+      <c r="M6" t="str">
+        <v>Pendiente_x000d_</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v/>
+        <v>6</v>
+      </c>
+      <c r="B7" t="str">
+        <v>J &amp; V Resguardo</v>
+      </c>
+      <c r="C7" t="str">
+        <v>alta</v>
+      </c>
+      <c r="D7" t="str">
+        <v>LIMA</v>
+      </c>
+      <c r="E7" t="str">
+        <v>29/05/2026</v>
+      </c>
+      <c r="F7" t="str">
+        <v>11:30-11:45</v>
+      </c>
+      <c r="G7" t="str">
+        <v>8/05/2026</v>
+      </c>
+      <c r="H7" t="str">
+        <v>INICIAL DE LICENCIA DE USO</v>
+      </c>
+      <c r="I7" t="str">
+        <v>76477494</v>
+      </c>
+      <c r="J7" t="str">
+        <v xml:space="preserve">052418-0 </v>
+      </c>
+      <c r="K7" t="str">
+        <v>CORTA</v>
+      </c>
+      <c r="L7" t="str">
+        <v>REVOLVER</v>
+      </c>
+      <c r="M7" t="str">
+        <v>Pendiente_x000d_</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
+        <v>7</v>
+      </c>
+      <c r="B8" t="str">
+        <v>J &amp; V Resguardo</v>
+      </c>
+      <c r="C8" t="str">
+        <v>alta</v>
+      </c>
+      <c r="D8" t="str">
+        <v>LIMA</v>
+      </c>
+      <c r="E8" t="str">
+        <v>29/05/2026</v>
+      </c>
+      <c r="F8" t="str">
+        <v>11:30-11:45</v>
+      </c>
+      <c r="G8" t="str">
+        <v>8/05/2026</v>
+      </c>
+      <c r="H8" t="str">
+        <v>INICIAL DE LICENCIA DE USO</v>
+      </c>
+      <c r="I8" t="str">
+        <v>76477494</v>
+      </c>
+      <c r="J8" t="str">
+        <v xml:space="preserve">052418-0 </v>
+      </c>
+      <c r="K8" t="str">
+        <v>LARGA</v>
+      </c>
+      <c r="L8" t="str">
+        <v>ESCOPETA</v>
+      </c>
+      <c r="M8" t="str">
+        <v>Pendiente_x000d_</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>8</v>
+      </c>
+      <c r="B9" t="str">
+        <v>J &amp; V Resguardo</v>
+      </c>
+      <c r="C9" t="str">
+        <v>alta</v>
+      </c>
+      <c r="D9" t="str">
+        <v>LIMA</v>
+      </c>
+      <c r="E9" t="str">
+        <v>29/05/2026</v>
+      </c>
+      <c r="F9" t="str">
+        <v>12:00-12:15</v>
+      </c>
+      <c r="G9" t="str">
+        <v>8/05/2026</v>
+      </c>
+      <c r="H9" t="str">
+        <v>RENOVACION DE LICENCIA DE USO</v>
+      </c>
+      <c r="I9" t="str">
+        <v>00966547</v>
+      </c>
+      <c r="J9" t="str">
+        <v>098412-0</v>
+      </c>
+      <c r="K9" t="str">
+        <v>CORTA</v>
+      </c>
+      <c r="L9" t="str">
+        <v>REVOLVER</v>
+      </c>
+      <c r="M9" t="str">
+        <v>Pendiente_x000d_</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N10"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/programaciones-armas.xlsx
+++ b/data/programaciones-armas.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -457,28 +457,28 @@
         <v>LIMA</v>
       </c>
       <c r="E2" t="str">
-        <v>29/05/2026</v>
+        <v>11/06/2026</v>
       </c>
       <c r="F2" t="str">
-        <v>08:00-08:15</v>
+        <v>12:30-12:45</v>
       </c>
       <c r="G2" t="str">
-        <v>8/05/2026</v>
+        <v>21/05/2026</v>
       </c>
       <c r="H2" t="str">
         <v>RENOVACION DE LICENCIA DE USO</v>
       </c>
       <c r="I2" t="str">
-        <v>09627091</v>
+        <v>77276891</v>
       </c>
       <c r="J2" t="str">
-        <v>060579-0</v>
+        <v>034550-0</v>
       </c>
       <c r="K2" t="str">
         <v>CORTA</v>
       </c>
       <c r="L2" t="str">
-        <v>PISTOLA</v>
+        <v>REVOLVER</v>
       </c>
       <c r="M2" t="str">
         <v>Pendiente_x000d_</v>
@@ -486,7 +486,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="str">
         <v>J &amp; V Resguardo</v>
@@ -498,28 +498,28 @@
         <v>LIMA</v>
       </c>
       <c r="E3" t="str">
-        <v>29/05/2026</v>
+        <v>11/06/2026</v>
       </c>
       <c r="F3" t="str">
-        <v>08:15-08:30</v>
+        <v>12:30-12:45</v>
       </c>
       <c r="G3" t="str">
-        <v>8/05/2026</v>
+        <v>21/05/2026</v>
       </c>
       <c r="H3" t="str">
         <v>RENOVACION DE LICENCIA DE USO</v>
       </c>
       <c r="I3" t="str">
-        <v>10198664</v>
+        <v>77276891</v>
       </c>
       <c r="J3" t="str">
-        <v>020858-0</v>
+        <v>034550-0</v>
       </c>
       <c r="K3" t="str">
-        <v>CORTA</v>
+        <v>LARGA</v>
       </c>
       <c r="L3" t="str">
-        <v>PISTOLA</v>
+        <v>ESCOPETA</v>
       </c>
       <c r="M3" t="str">
         <v>Pendiente_x000d_</v>
@@ -527,7 +527,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B4" t="str">
         <v>J &amp; V Resguardo</v>
@@ -539,22 +539,22 @@
         <v>LIMA</v>
       </c>
       <c r="E4" t="str">
-        <v>29/05/2026</v>
+        <v>11/06/2026</v>
       </c>
       <c r="F4" t="str">
-        <v>09:00-09:15</v>
+        <v>12:30-12:45</v>
       </c>
       <c r="G4" t="str">
-        <v>8/05/2026</v>
+        <v>21/05/2026</v>
       </c>
       <c r="H4" t="str">
         <v>RENOVACION DE LICENCIA DE USO</v>
       </c>
       <c r="I4" t="str">
-        <v>10439677</v>
+        <v>74388142</v>
       </c>
       <c r="J4" t="str">
-        <v>099009-0</v>
+        <v>028816-0</v>
       </c>
       <c r="K4" t="str">
         <v>CORTA</v>
@@ -568,7 +568,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" t="str">
         <v>J &amp; V Resguardo</v>
@@ -580,22 +580,22 @@
         <v>LIMA</v>
       </c>
       <c r="E5" t="str">
-        <v>29/05/2026</v>
+        <v>11/06/2026</v>
       </c>
       <c r="F5" t="str">
-        <v>11:15-11:30</v>
+        <v>12:15-12:30</v>
       </c>
       <c r="G5" t="str">
-        <v>8/05/2026</v>
+        <v>21/05/2026</v>
       </c>
       <c r="H5" t="str">
-        <v>INICIAL DE LICENCIA DE USO</v>
+        <v>RENOVACION DE LICENCIA DE USO</v>
       </c>
       <c r="I5" t="str">
-        <v>78997430</v>
+        <v>62160619</v>
       </c>
       <c r="J5" t="str">
-        <v>100403-0</v>
+        <v>028818-0</v>
       </c>
       <c r="K5" t="str">
         <v>CORTA</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6" t="str">
         <v>J &amp; V Resguardo</v>
@@ -621,22 +621,22 @@
         <v>LIMA</v>
       </c>
       <c r="E6" t="str">
-        <v>29/05/2026</v>
+        <v>11/06/2026</v>
       </c>
       <c r="F6" t="str">
-        <v>11:15-11:30</v>
+        <v>12:15-12:30</v>
       </c>
       <c r="G6" t="str">
-        <v>8/05/2026</v>
+        <v>21/05/2026</v>
       </c>
       <c r="H6" t="str">
-        <v>INICIAL DE LICENCIA DE USO</v>
+        <v>RENOVACION DE LICENCIA DE USO</v>
       </c>
       <c r="I6" t="str">
-        <v>78997430</v>
+        <v>62160619</v>
       </c>
       <c r="J6" t="str">
-        <v>100403-0</v>
+        <v>028818-0</v>
       </c>
       <c r="K6" t="str">
         <v>LARGA</v>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" t="str">
         <v>J &amp; V Resguardo</v>
@@ -662,22 +662,22 @@
         <v>LIMA</v>
       </c>
       <c r="E7" t="str">
-        <v>29/05/2026</v>
+        <v>11/06/2026</v>
       </c>
       <c r="F7" t="str">
-        <v>11:30-11:45</v>
+        <v>12:00-12:15</v>
       </c>
       <c r="G7" t="str">
-        <v>8/05/2026</v>
+        <v>21/05/2026</v>
       </c>
       <c r="H7" t="str">
-        <v>INICIAL DE LICENCIA DE USO</v>
+        <v>RENOVACION DE LICENCIA DE USO</v>
       </c>
       <c r="I7" t="str">
-        <v>76477494</v>
+        <v>43507007</v>
       </c>
       <c r="J7" t="str">
-        <v xml:space="preserve">052418-0 </v>
+        <v>008895-0</v>
       </c>
       <c r="K7" t="str">
         <v>CORTA</v>
@@ -691,7 +691,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B8" t="str">
         <v>J &amp; V Resguardo</v>
@@ -703,22 +703,22 @@
         <v>LIMA</v>
       </c>
       <c r="E8" t="str">
-        <v>29/05/2026</v>
+        <v>11/06/2026</v>
       </c>
       <c r="F8" t="str">
-        <v>11:30-11:45</v>
+        <v>12:00-12:15</v>
       </c>
       <c r="G8" t="str">
-        <v>8/05/2026</v>
+        <v>21/05/2026</v>
       </c>
       <c r="H8" t="str">
-        <v>INICIAL DE LICENCIA DE USO</v>
+        <v>RENOVACION DE LICENCIA DE USO</v>
       </c>
       <c r="I8" t="str">
-        <v>76477494</v>
+        <v>43507007</v>
       </c>
       <c r="J8" t="str">
-        <v xml:space="preserve">052418-0 </v>
+        <v>008895-0</v>
       </c>
       <c r="K8" t="str">
         <v>LARGA</v>
@@ -732,7 +732,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B9" t="str">
         <v>J &amp; V Resguardo</v>
@@ -744,22 +744,22 @@
         <v>LIMA</v>
       </c>
       <c r="E9" t="str">
-        <v>29/05/2026</v>
+        <v>11/06/2026</v>
       </c>
       <c r="F9" t="str">
-        <v>12:00-12:15</v>
+        <v>12:15-12:30</v>
       </c>
       <c r="G9" t="str">
-        <v>8/05/2026</v>
+        <v>21/05/2026</v>
       </c>
       <c r="H9" t="str">
         <v>RENOVACION DE LICENCIA DE USO</v>
       </c>
       <c r="I9" t="str">
-        <v>00966547</v>
+        <v>40016403</v>
       </c>
       <c r="J9" t="str">
-        <v>098412-0</v>
+        <v>008896-0</v>
       </c>
       <c r="K9" t="str">
         <v>CORTA</v>
@@ -773,12 +773,53 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
+        <v>5</v>
+      </c>
+      <c r="B10" t="str">
+        <v>J &amp; V Resguardo</v>
+      </c>
+      <c r="C10" t="str">
+        <v>alta</v>
+      </c>
+      <c r="D10" t="str">
+        <v>LIMA</v>
+      </c>
+      <c r="E10" t="str">
+        <v>11/06/2026</v>
+      </c>
+      <c r="F10" t="str">
+        <v>12:15-12:30</v>
+      </c>
+      <c r="G10" t="str">
+        <v>21/05/2026</v>
+      </c>
+      <c r="H10" t="str">
+        <v>RENOVACION DE LICENCIA DE USO</v>
+      </c>
+      <c r="I10" t="str">
+        <v>40016403</v>
+      </c>
+      <c r="J10" t="str">
+        <v>008896-0</v>
+      </c>
+      <c r="K10" t="str">
+        <v>LARGA</v>
+      </c>
+      <c r="L10" t="str">
+        <v>ESCOPETA</v>
+      </c>
+      <c r="M10" t="str">
+        <v>Pendiente_x000d_</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/programaciones-armas.xlsx
+++ b/data/programaciones-armas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fserrano\Desktop\ARMAS-GADSO-1.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D215E84-969C-4145-B194-D9F07731E5D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DC28577-F666-4F66-BF17-625F9B016F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3048" yWindow="3036" windowWidth="17268" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="42">
   <si>
     <t>id_registro</t>
   </si>
@@ -73,50 +73,86 @@
     <t>alta</t>
   </si>
   <si>
-    <t>JEFATURA ZONAL DE JUNIN</t>
-  </si>
-  <si>
-    <t>10/06/2026</t>
-  </si>
-  <si>
-    <t>12:30-12:45</t>
+    <t>CORTA</t>
+  </si>
+  <si>
+    <t>Pendiente</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>LIMA</t>
+  </si>
+  <si>
+    <t>REVOLVER</t>
+  </si>
+  <si>
+    <t>2</t>
   </si>
   <si>
     <t>INICIAL DE LICENCIA DE USO</t>
   </si>
   <si>
-    <t>73208098</t>
-  </si>
-  <si>
-    <t>038542-0</t>
-  </si>
-  <si>
-    <t>CORTA</t>
+    <t>LARGA</t>
+  </si>
+  <si>
+    <t>ESCOPETA</t>
+  </si>
+  <si>
+    <t>12:00-12:15</t>
+  </si>
+  <si>
+    <t>12:15-12:30</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>RENOVACION DE LICENCIA DE USO</t>
+  </si>
+  <si>
+    <t>41029284</t>
+  </si>
+  <si>
+    <t>080451-0</t>
+  </si>
+  <si>
+    <t>11:30-11:45</t>
   </si>
   <si>
     <t>PISTOLA</t>
   </si>
   <si>
-    <t>Pendiente</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>LARGA</t>
-  </si>
-  <si>
-    <t>ESCOPETA</t>
-  </si>
-  <si>
-    <t/>
+    <t>48067334</t>
+  </si>
+  <si>
+    <t>057485-0</t>
+  </si>
+  <si>
+    <t>43507007</t>
+  </si>
+  <si>
+    <t>064682-0</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>12:45-13:00</t>
+  </si>
+  <si>
+    <t>70275498</t>
+  </si>
+  <si>
+    <t>071375-0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -125,8 +161,91 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="12"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -150,16 +269,49 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="10"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="10" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="10" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="11"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="11" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="11" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="13"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="13" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="13" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="14">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 10" xfId="9" xr:uid="{9F2AE7A4-AEA5-488E-A697-34EBEA1F5AC4}"/>
+    <cellStyle name="Normal 11" xfId="10" xr:uid="{56E6BAD8-385D-4526-9A7F-1B17EA1B1051}"/>
+    <cellStyle name="Normal 12" xfId="11" xr:uid="{1353AE2B-EE64-4825-9144-744603C912E8}"/>
+    <cellStyle name="Normal 13" xfId="12" xr:uid="{447F4DB1-8B34-41FC-9585-5B9ED4CF1713}"/>
+    <cellStyle name="Normal 14" xfId="13" xr:uid="{4FAED0F0-E317-4FE2-99BA-3CA9CA93B1D5}"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{F73B2141-8F1A-46E0-A6FF-C2277354502D}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{8716200F-0A19-4BE3-8F2A-389E2E69B52A}"/>
+    <cellStyle name="Normal 4" xfId="3" xr:uid="{85BA6668-D1D6-4E2E-9842-E65555C939A2}"/>
+    <cellStyle name="Normal 5" xfId="4" xr:uid="{23606440-F7FD-40E4-B32D-2E19E0C0C100}"/>
+    <cellStyle name="Normal 6" xfId="5" xr:uid="{D2C8A61F-5085-431F-BA0A-C06B259F5AD9}"/>
+    <cellStyle name="Normal 7" xfId="6" xr:uid="{869481F6-4167-49D3-97D5-BB548E4F794E}"/>
+    <cellStyle name="Normal 8" xfId="7" xr:uid="{2CEE9224-08BB-4136-8A76-5558C8FC60C9}"/>
+    <cellStyle name="Normal 9" xfId="8" xr:uid="{D830092F-3B6F-4ABB-B7FF-ED79A833394B}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
@@ -497,9 +649,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -543,100 +695,239 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="9">
+        <v>46237</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" s="9">
+        <v>46217</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="9">
+        <v>46237</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G3" s="9">
+        <v>46217</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="K3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
+      <c r="L3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F2" t="s">
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="9">
+        <v>46237</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="9">
+        <v>46217</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E5" s="9">
+        <v>46237</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="9">
+        <v>46217</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="5"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="5"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8" s="5"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>19</v>
-      </c>
-      <c r="G2" s="1">
-        <v>46169</v>
-      </c>
-      <c r="H2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
-      </c>
-      <c r="K2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="1">
-        <v>46183</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" s="1">
-        <v>46169</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L3" t="s">
-        <v>28</v>
-      </c>
-      <c r="M3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="G6" s="2"/>
-    </row>
-    <row r="13" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:N1 A4:N13 A3:D3 F3 A2:F2 H2:N2 H3:N3" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:N1 A10:N13 N2:N6 N7 N8 N9" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/programaciones-armas.xlsx
+++ b/data/programaciones-armas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fserrano\Desktop\ARMAS-GADSO-1.0\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DC28577-F666-4F66-BF17-625F9B016F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77AC99E9-14E1-4334-8CBF-9FD49DF066A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3048" yWindow="3036" windowWidth="17268" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>id_registro</t>
   </si>
@@ -82,77 +82,29 @@
     <t/>
   </si>
   <si>
-    <t>LIMA</t>
-  </si>
-  <si>
     <t>REVOLVER</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>INICIAL DE LICENCIA DE USO</t>
-  </si>
-  <si>
-    <t>LARGA</t>
-  </si>
-  <si>
-    <t>ESCOPETA</t>
-  </si>
-  <si>
-    <t>12:00-12:15</t>
-  </si>
-  <si>
-    <t>12:15-12:30</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>RENOVACION DE LICENCIA DE USO</t>
-  </si>
-  <si>
-    <t>41029284</t>
-  </si>
-  <si>
-    <t>080451-0</t>
-  </si>
-  <si>
-    <t>11:30-11:45</t>
-  </si>
-  <si>
-    <t>PISTOLA</t>
-  </si>
-  <si>
-    <t>48067334</t>
-  </si>
-  <si>
-    <t>057485-0</t>
-  </si>
-  <si>
-    <t>43507007</t>
-  </si>
-  <si>
-    <t>064682-0</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>12:45-13:00</t>
-  </si>
-  <si>
-    <t>70275498</t>
-  </si>
-  <si>
-    <t>071375-0</t>
+    <t>RENOVACIÓN DE LICENCIA DE USO</t>
+  </si>
+  <si>
+    <t>73445455</t>
+  </si>
+  <si>
+    <t>104102-0</t>
+  </si>
+  <si>
+    <t>JEFATURA ZONAL LAMBAYEQUE (EX-INTENDENCIA II NORTE)</t>
+  </si>
+  <si>
+    <t>9:15-9:30</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -245,6 +197,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -269,8 +236,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="14">
+  <cellStyleXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
@@ -285,25 +253,31 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="10"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="10" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="10" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="11"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="11" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="11" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="13"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="13" applyNumberFormat="1"/>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="13" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="10"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="10" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="10" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="11"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="11" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="11" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="13"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="13" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="13" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="14"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="14" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="14" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="10" applyFont="1"/>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="14">
+  <cellStyles count="15">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 10" xfId="9" xr:uid="{9F2AE7A4-AEA5-488E-A697-34EBEA1F5AC4}"/>
     <cellStyle name="Normal 11" xfId="10" xr:uid="{56E6BAD8-385D-4526-9A7F-1B17EA1B1051}"/>
     <cellStyle name="Normal 12" xfId="11" xr:uid="{1353AE2B-EE64-4825-9144-744603C912E8}"/>
     <cellStyle name="Normal 13" xfId="12" xr:uid="{447F4DB1-8B34-41FC-9585-5B9ED4CF1713}"/>
     <cellStyle name="Normal 14" xfId="13" xr:uid="{4FAED0F0-E317-4FE2-99BA-3CA9CA93B1D5}"/>
+    <cellStyle name="Normal 15" xfId="14" xr:uid="{DFA1382E-8F99-43DF-83BD-57449C503719}"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{F73B2141-8F1A-46E0-A6FF-C2277354502D}"/>
     <cellStyle name="Normal 3" xfId="2" xr:uid="{8716200F-0A19-4BE3-8F2A-389E2E69B52A}"/>
     <cellStyle name="Normal 4" xfId="3" xr:uid="{85BA6668-D1D6-4E2E-9842-E65555C939A2}"/>
@@ -696,168 +670,90 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="12">
+        <v>46275</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="12">
+        <v>46273</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="9">
-        <v>46237</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G2" s="9">
-        <v>46217</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2" s="7" t="s">
+      <c r="M2" s="10" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="9">
-        <v>46237</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" s="9">
-        <v>46217</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L3" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" s="7" t="s">
-        <v>18</v>
-      </c>
+      <c r="A3" s="8"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="7"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="9">
-        <v>46237</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="9">
-        <v>46217</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="K4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>18</v>
-      </c>
+      <c r="A4" s="8"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="9">
-        <v>46237</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G5" s="9">
-        <v>46217</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="J5" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>18</v>
-      </c>
+      <c r="A5" s="8"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="7"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
@@ -894,7 +790,7 @@
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
-      <c r="E8" s="6"/>
+      <c r="E8" s="14"/>
       <c r="F8" s="4"/>
       <c r="G8" s="6"/>
       <c r="H8" s="4"/>
@@ -907,7 +803,7 @@
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A9" s="2"/>
       <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
+      <c r="C9" s="13"/>
       <c r="D9" s="1"/>
       <c r="E9" s="3"/>
       <c r="F9" s="1"/>
@@ -926,6 +822,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
     <ignoredError sqref="A1:N1 A10:N13 N2:N6 N7 N8 N9" numberStoredAsText="1"/>
   </ignoredErrors>
